--- a/doc/詳細設計/02_画面詳細設計/SCR-003_勤怠一覧画面.xlsx
+++ b/doc/詳細設計/02_画面詳細設計/SCR-003_勤怠一覧画面.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="基本情報" sheetId="1" state="visible" r:id="rId3"/>
@@ -55,12 +55,18 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2A6099"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -97,8 +103,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -111,7 +121,110 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>149760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>561960</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>27720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="画像 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="812880" y="325080"/>
+          <a:ext cx="11941200" cy="6217920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -311,7 +424,9 @@
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -319,6 +434,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffffページ &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
